--- a/results/job_matches_2026-08-27.xlsx
+++ b/results/job_matches_2026-08-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,105 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer-Anthropic-US East</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>United Wheels Inc.</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miamisburg, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27e79ad2e915711e</t>
+          <t>https://www.indeed.com/viewjob?jk=e38dcb9b17b16495</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer-Anthropic-US West</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, Hadoop</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ced4229e6a8ce7e</t>
+          <t>https://www.indeed.com/viewjob?jk=669da4f7162d9233</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Starburst / Apache Trino</t>
+          <t>AI Platform Engineer-Anthropic-US East</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3927b1ab23dc839</t>
+          <t>https://www.indeed.com/viewjob?jk=fec3742f5627ce31</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ProArch</t>
+          <t>United Wheels Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miamisburg, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
+          <t>https://www.indeed.com/viewjob?jk=27e79ad2e915711e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Backend Developer - Chicago</t>
+          <t>Cloud Transformation Senior Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23172e882a0d58c</t>
+          <t>https://www.indeed.com/viewjob?jk=d23da9f70702c22b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Database Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da35022772d82448</t>
+          <t>https://www.indeed.com/viewjob?jk=7ced4229e6a8ce7e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Backend Developer with Digital Banking exp.</t>
+          <t>Senior Data Engineer — Starburst / Apache Trino</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Triade Flevoland</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975335ad394cec71</t>
+          <t>https://www.indeed.com/viewjob?jk=f3927b1ab23dc839</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ProArch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
+          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Back End Go Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Beverly, MA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd5bd8233720a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc2fd48ea54d930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bally's Intralot</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776d0f6fa809d94b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b59973a58a51a68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Connect Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>One Park Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70704f843af03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a224f58d51b5650</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=d548d7422fee5742</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Spark Streaming, Kafka</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba92a5e620a7d4de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Grade C1</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5adae439689ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=2830b916627ff463</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8edfe30abb7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf63850f9b450b4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP BTP CPI integration developer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>www.prolim.com</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b9d3edeebc6d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8cd33436667375</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1337a2df075881</t>
+          <t>https://www.indeed.com/viewjob?jk=ac42457f871f6f2b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601078fca17d6436</t>
+          <t>https://www.indeed.com/viewjob?jk=dfad47bd4cd04de0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36469ab073779d</t>
+          <t>https://www.indeed.com/viewjob?jk=9490256d6d1e6ac3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=a93b6a8461258317</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Prinicipal, Data Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, Power BI, Tableau, DataOps</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8e82e7462392e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee45fef9ca01bb4d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be897c625ddfe98</t>
+          <t>https://www.indeed.com/viewjob?jk=cae27600d6dd1a97</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wolfe, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, BigQuery, Spark, Snowflake</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e8240a360be575</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2a5b31485e2292</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=4dda7256d2d7c901</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=967e37ab9b2dc5bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5686a0b8163a717</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b029b57bd1664e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
+          <t>https://www.indeed.com/viewjob?jk=8e25696fbfffc446</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
+          <t>https://www.indeed.com/viewjob?jk=b70bc1a487b4331d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
+          <t>https://www.indeed.com/viewjob?jk=307d3cf60326dbf5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Development Systems Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07c88e14adbffe5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product - SF Only</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d84038cb57e54e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca40c7722a95e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4854936f22694575</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6e427e88678150</t>
+          <t>https://www.indeed.com/viewjob?jk=807ac4fc7fe90232</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=8e29b7b6e690204f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9ec8de823c6860</t>
+          <t>https://www.indeed.com/viewjob?jk=449571831b7901e5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data &amp; AI Solution Architect</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91e091efc59de7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MetTel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,172 +1756,172 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
+          <t>https://www.indeed.com/viewjob?jk=eeffca236bc804b3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote)</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca683f10163f215e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f7621eed158a8c3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Platform Software Engineer — Global Connected Vehicle Platform</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8aabfc80480cb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4faf9ee14d5944</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46ae133ecb4f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d2ab456c735aef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4279ea6cf6b731ec</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f40f8ae5a2bc0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a58dc24f0f93b419</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Snowflake Consultant</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Time Travel, Data Modeling, ETL</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c00b7ca002be65</t>
+          <t>https://www.indeed.com/viewjob?jk=b7870d91d6f2bf4a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Platform</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Databricks, Scala, Kafka, Snowflake, dbt</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c3fd73c78e94d5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5c435f75d8a0c6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, BigQuery, Scala, Data Modeling, Dimensional Modeling, dbt</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
+          <t>https://www.indeed.com/viewjob?jk=95789a34111441ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack - UI</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Swisslog Healthcare AG Branche NL</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c9e14eaa0d3f83</t>
+          <t>https://www.indeed.com/viewjob?jk=a06f30c1a1ff123e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Database Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Swisslog Healthcare</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4301843c7a7136de</t>
+          <t>https://www.indeed.com/viewjob?jk=da35022772d82448</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Java Backend Developer with Digital Banking exp.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca81c7c676de2370</t>
+          <t>https://www.indeed.com/viewjob?jk=975335ad394cec71</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Solution Architect - Azure Data Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, HDFS, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4829c9bbd0347b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac7f22d45fe6fb2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=742fd0f2c5e489a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e8380cd9e35b2546</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Integrations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3fdb949b913773</t>
+          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - Databricks</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beverly, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabe2481c213ffb1</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd5bd8233720a0a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Metova</t>
+          <t>Bally's Intralot</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Time Travel, Dimensional Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc3b7ca4d2a8d47</t>
+          <t>https://www.indeed.com/viewjob?jk=776d0f6fa809d94b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Connect Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>One Park Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c84b17d624f68f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d70704f843af03d8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisor, Enterprise Solution Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pyxis Management Consulting Group</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Terraform, Airflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df510917e20222b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f24a48e79605724</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e83403aef0eb985</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Senior Data Engineer Grade C1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5adae439689ed8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Azure Solutions Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lobel Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db6ac7cf2f086e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf33c5c43beaa8e6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer 2</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f6e507178eea68</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f41a995f505d3c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer / Data Solutions Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe843336b1995ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1337a2df075881</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Spark, Kafka, Oracle, MySQL, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61baaa99648fbaa6</t>
+          <t>https://www.indeed.com/viewjob?jk=601078fca17d6436</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data &amp; AI Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141f9d385a079193</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36469ab073779d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Analytics Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, MLOps</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dbe830bdc25c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1df95cde0f30cf72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, MLOps, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd8bdf82d729ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd55676debc3fc4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Prinicipal, Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8e82e7462392e7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f8171dad79d797d</t>
+          <t>https://www.indeed.com/viewjob?jk=4be897c625ddfe98</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Wolfe, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd6170b836318a3</t>
+          <t>https://www.indeed.com/viewjob?jk=55e8240a360be575</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Charlotte)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbae05545c6868d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5390342666784d7e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Chicago)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,137 +2876,137 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f0621a423908c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5686a0b8163a717</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer BILH Pharmacy Westwood, Ma, Hybrid / on-site</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Beth Israel Lahey Health</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westwood, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Data Modeling, ETL, Kubernetes, AKS, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf255b6550fc872f</t>
+          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Unity Catalog, Spark</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
+          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Infrastructure Automation Engineer</t>
+          <t>Senior Engineer, Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tapestry</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Spark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a7770f9ee523e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Development Systems Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d618dcf278adc42</t>
+          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Data Product - SF Only</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae136048a3d8779</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Connected Vehicle Platform Engineer</t>
+          <t>Senior Developer, Sales Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Textron Specialized Vehicles</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, ETL, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
+          <t>https://www.indeed.com/viewjob?jk=233d88dbe3d74b1b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Full Stack .NET / Angular Developer (contract)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab0af7df8344321b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c718b7484abad21</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f79db46ebbc9c81b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
+          <t>https://www.indeed.com/viewjob?jk=0dca40c7722a95e0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9ec8de823c6860</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Sr Data &amp; AI Solution Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,172 +3261,172 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
+          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Collectiv LLC</t>
+          <t>MetTel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e76c61522acf68</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3950e40095baf48</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e3a98c4a637877</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46ae133ecb4f7e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Sr. Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, Athena, S3, RDS, Databricks, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=13c3fd73c78e94d5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI LLM Engineer</t>
+          <t>Software Engineer - Full Stack - UI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Swisslog Healthcare AG Branche NL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512d71dc2c72b295</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c9e14eaa0d3f83</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer II</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Swisslog Healthcare</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,42 +3471,1547 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97be22e6059d1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4301843c7a7136de</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Application Engineer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SidhSol</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f40f8ae5a2bc0ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MuleSoft Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca81c7c676de2370</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Business Consultant - AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4829c9bbd0347b9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Business Consultant - AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=742fd0f2c5e489a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Engineer I- Software</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868097f3e1f3cce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Malibu Boats</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Loudon, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f64a79707aee64aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c35234a1a55ade1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IT Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Shoals Technologies Group</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Portland, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9437463b88914f0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Integrations Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sherwin-Williams</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf3fdb949b913773</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Azure Data Engineer - Databricks</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Alchemy</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aabe2481c213ffb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Metova</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Snowflake, Time Travel, Dimensional Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc3b7ca4d2a8d47</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c84b17d624f68f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Developer 2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BLOC Resources, LLC</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f6e507178eea68</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Fintech</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36d6cd0794dbf11e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Oracle, ETL, ELT, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb99c3f8ead0f44</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Spark, Kafka, Oracle, MySQL, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61baaa99648fbaa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sr. Data &amp; Analytics Architect</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Grocery Outlet</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Emeryville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
         <v>10.4</v>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ff332af76c49db</t>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dbe830bdc25c0e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801b07c086fc4c1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, MLOps, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdd8bdf82d729ef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f8171dad79d797d</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CleanSlate Technology Group</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dd6170b836318a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Charlotte)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbae05545c6868d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Chicago)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef6f0621a423908c</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer BILH Pharmacy Westwood, Ma, Hybrid / on-site</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Beth Israel Lahey Health</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Westwood, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, Data Modeling, ETL, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf255b6550fc872f</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Abbott Park, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Unity Catalog, Spark</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Infrastructure Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Tapestry</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Spark, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18a7770f9ee523e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d618dcf278adc42</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cae136048a3d8779</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Connected Vehicle Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Textron Specialized Vehicles</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, Scala, ETL, MLOps, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Shoals Technologies Group</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Portland, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b08e7f2c8d072fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Associate Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Lockton Companies</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>S3, IAM, RDS, Databricks, Scala, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e522678fc742dc7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fe925ed625c1711</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3950e40095baf48</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Collectiv LLC</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47e76c61522acf68</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Security Analyst</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98920657e7b757a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AI LLM Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Siemens Healthineers</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=512d71dc2c72b295</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6875238a4eff9e2d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-27.xlsx
+++ b/results/job_matches_2026-08-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,87 +573,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Big Data Engineer – Hadoop / AWS EMR, Spark + Scala &amp; Kafka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>United Wheels Inc.</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miamisburg, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27e79ad2e915711e</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ac65065c216ba1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Transformation Senior Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23da9f70702c22b</t>
+          <t>https://www.indeed.com/viewjob?jk=477b756caf879e2b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer — Starburst / Apache Trino</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Triade Flevoland</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, Hadoop</t>
+          <t>AWS, S3, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ced4229e6a8ce7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3927b1ab23dc839</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Starburst / Apache Trino</t>
+          <t>Software Development Engineer I - AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,104 +696,104 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, ECS, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3927b1ab23dc839</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5738d386244e74</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Devops Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ProArch</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
+          <t>https://www.indeed.com/viewjob?jk=ce68c41a7d1fadf5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Back End Go Developer</t>
+          <t>Senior Engineer, Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Blob Storage, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc2fd48ea54d930</t>
+          <t>https://www.indeed.com/viewjob?jk=9610995ca15527f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fabric Architect</t>
+          <t>Back End Go Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b59973a58a51a68</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc2fd48ea54d930</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a224f58d51b5650</t>
+          <t>https://www.indeed.com/viewjob?jk=7b59973a58a51a68</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d548d7422fee5742</t>
+          <t>https://www.indeed.com/viewjob?jk=8a224f58d51b5650</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba92a5e620a7d4de</t>
+          <t>https://www.indeed.com/viewjob?jk=d548d7422fee5742</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2830b916627ff463</t>
+          <t>https://www.indeed.com/viewjob?jk=ba92a5e620a7d4de</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf63850f9b450b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2830b916627ff463</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8cd33436667375</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf63850f9b450b4</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac42457f871f6f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8cd33436667375</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfad47bd4cd04de0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac42457f871f6f2b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9490256d6d1e6ac3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfad47bd4cd04de0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93b6a8461258317</t>
+          <t>https://www.indeed.com/viewjob?jk=9490256d6d1e6ac3</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee45fef9ca01bb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a93b6a8461258317</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae27600d6dd1a97</t>
+          <t>https://www.indeed.com/viewjob?jk=ee45fef9ca01bb4d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2a5b31485e2292</t>
+          <t>https://www.indeed.com/viewjob?jk=cae27600d6dd1a97</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dda7256d2d7c901</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2a5b31485e2292</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=967e37ab9b2dc5bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4dda7256d2d7c901</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3b029b57bd1664e</t>
+          <t>https://www.indeed.com/viewjob?jk=967e37ab9b2dc5bd</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e25696fbfffc446</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b029b57bd1664e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70bc1a487b4331d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e25696fbfffc446</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307d3cf60326dbf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b70bc1a487b4331d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07c88e14adbffe5</t>
+          <t>https://www.indeed.com/viewjob?jk=307d3cf60326dbf5</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d84038cb57e54e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07c88e14adbffe5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4854936f22694575</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d84038cb57e54e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807ac4fc7fe90232</t>
+          <t>https://www.indeed.com/viewjob?jk=4854936f22694575</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e29b7b6e690204f</t>
+          <t>https://www.indeed.com/viewjob?jk=807ac4fc7fe90232</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449571831b7901e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e29b7b6e690204f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91e091efc59de7</t>
+          <t>https://www.indeed.com/viewjob?jk=449571831b7901e5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeffca236bc804b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91e091efc59de7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f7621eed158a8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=eeffca236bc804b3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4faf9ee14d5944</t>
+          <t>https://www.indeed.com/viewjob?jk=3f7621eed158a8c3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d2ab456c735aef</t>
+          <t>https://www.indeed.com/viewjob?jk=de4faf9ee14d5944</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4279ea6cf6b731ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d2ab456c735aef</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58dc24f0f93b419</t>
+          <t>https://www.indeed.com/viewjob?jk=4279ea6cf6b731ec</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7870d91d6f2bf4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a58dc24f0f93b419</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd5c435f75d8a0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7870d91d6f2bf4a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95789a34111441ac</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5c435f75d8a0c6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06f30c1a1ff123e</t>
+          <t>https://www.indeed.com/viewjob?jk=95789a34111441ac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Database Architect</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>Redshift, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,129 +2106,129 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da35022772d82448</t>
+          <t>https://www.indeed.com/viewjob?jk=a06f30c1a1ff123e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Backend Developer with Digital Banking exp.</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aircall</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, ECS, IAM, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975335ad394cec71</t>
+          <t>https://www.indeed.com/viewjob?jk=b340560c384cf691</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect - Azure Data Analytics</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, HDFS, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, ECS, IAM, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac7f22d45fe6fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb602e905cf8e618</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8380cd9e35b2546</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a0d061adef57ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,77 +2236,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
+          <t>https://www.indeed.com/viewjob?jk=cadd1b7c846571a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Beverly, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd5bd8233720a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=cecaeb7f30f5319a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bally's Intralot</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776d0f6fa809d94b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8380cd9e35b2546</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Connect Engineer</t>
+          <t>Data Engineer / Dev Ops Engineer (Entry-level)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>One Park Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70704f843af03d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c74dd3c01bed4e6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Advisor, Enterprise Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Tillys</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f24a48e79605724</t>
+          <t>https://www.indeed.com/viewjob?jk=cff22505a47f4228</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,77 +2411,77 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e83403aef0eb985</t>
+          <t>https://www.indeed.com/viewjob?jk=2e40611058ee4416</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Grade C1</t>
+          <t>BI / Data Architect (Remote)-2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5adae439689ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f7d469fb566b4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf33c5c43beaa8e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e83403aef0eb985</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Northwood Investors</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f41a995f505d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2347d9cb82b32b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1337a2df075881</t>
+          <t>https://www.indeed.com/viewjob?jk=1df95cde0f30cf72</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,129 +2596,129 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601078fca17d6436</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd55676debc3fc4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>NationsBenefits</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36469ab073779d</t>
+          <t>https://www.indeed.com/viewjob?jk=0137050565978d38</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, GCP, Spark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df95cde0f30cf72</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d4d4ff843dddd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd55676debc3fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=ed654d6987db5d87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Prinicipal, Data Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8e82e7462392e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3cfce3fc392b166a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Database Administrator III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,104 +2761,104 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be897c625ddfe98</t>
+          <t>https://www.indeed.com/viewjob?jk=ba70fd5fe4fff929</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wolfe, LLC</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, IAM, RDS, BigQuery, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e8240a360be575</t>
+          <t>https://www.indeed.com/viewjob?jk=e74e8ed1040b80da</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>MetLife Legal Plans</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5390342666784d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b49427628ff5f7b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5686a0b8163a717</t>
+          <t>https://www.indeed.com/viewjob?jk=57257275c845106a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Data Engineer-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
+          <t>https://www.indeed.com/viewjob?jk=be8d80e3db1ec37c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Senior Software Engineer, Data Product - SF Only</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
+          <t>https://www.indeed.com/viewjob?jk=88adb284a479dd50</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Development Systems Engineer</t>
+          <t>Sr Software Engineer, DevOps</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae1383c636ae49c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Product - SF Only</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f79db46ebbc9c81b</t>
         </is>
       </c>
     </row>
@@ -3128,122 +3128,122 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79db46ebbc9c81b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf874fcd29625031</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Horizon Hobby LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dca40c7722a95e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4c7147702d5d61</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9ec8de823c6860</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e3a98c4a637877</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data &amp; AI Solution Architect</t>
+          <t>Software Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
+          <t>https://www.indeed.com/viewjob?jk=c213cb94949a31dc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MetTel</t>
+          <t>NationsBenefits</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4dfb0e7ccd153c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e3a98c4a637877</t>
+          <t>https://www.indeed.com/viewjob?jk=3f40f8ae5a2bc0ae</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46ae133ecb4f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=83f68e58416a70ba</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Platform</t>
+          <t>IT Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>State of Idaho</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,244 +3391,244 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Databricks, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c3fd73c78e94d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b09dbfb68572</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack - UI</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Swisslog Healthcare AG Branche NL</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c9e14eaa0d3f83</t>
+          <t>https://www.indeed.com/viewjob?jk=235a31caf915f203</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer - Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Swisslog Healthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4301843c7a7136de</t>
+          <t>https://www.indeed.com/viewjob?jk=f7976cb1e54d6a15</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f40f8ae5a2bc0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5757314c4e84a8bc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Engineer</t>
+          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Data Modeling, ETL, CI/CD, Maven, Kubernetes, SonarQube, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca81c7c676de2370</t>
+          <t>https://www.indeed.com/viewjob?jk=375c331d3616c79b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4829c9bbd0347b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=90158ba06c45fb12</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=742fd0f2c5e489a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b25e04a518ccf371</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>Microbiologist IV (Genomic Data Engineer)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, Scala, ETL, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868097f3e1f3cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=52da99c6b639f191</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Malibu Boats</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Loudon, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64a79707aee64aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1395ced7e9246546</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Software Engineer, Data, AI &amp; UX</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>ENGELHART</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c35234a1a55ade1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3a1157126f827c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>Malibu Boats</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Loudon, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9437463b88914f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f64a79707aee64aa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Integrations Engineer</t>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3fdb949b913773</t>
+          <t>https://www.indeed.com/viewjob?jk=8c35234a1a55ade1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - Databricks</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Shoals Technologies Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabe2481c213ffb1</t>
+          <t>https://www.indeed.com/viewjob?jk=9437463b88914f0b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Integrations Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Metova</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Time Travel, Dimensional Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc3b7ca4d2a8d47</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3fdb949b913773</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Azure Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c84b17d624f68f3</t>
+          <t>https://www.indeed.com/viewjob?jk=aabe2481c213ffb1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Sr. Associate, Software Automation Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, NoSQL, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
+          <t>https://www.indeed.com/viewjob?jk=82e24bf500bf974d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
+          <t>https://www.indeed.com/viewjob?jk=144d376d71f5a569</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Developer 2</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f6e507178eea68</t>
+          <t>https://www.indeed.com/viewjob?jk=1a12d319275ed2e2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d6cd0794dbf11e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3cb07a13330396</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, ETL, ELT, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb99c3f8ead0f44</t>
+          <t>https://www.indeed.com/viewjob?jk=136d8f78fd006971</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,42 +4091,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Spark, Kafka, Oracle, MySQL, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61baaa99648fbaa6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f2736a3fb27f5c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Analytics Architect</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,164 +4136,164 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dbe830bdc25c0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=33dec0fb23b87e90</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801b07c086fc4c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=0bae9c23ab2afa14</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, MLOps, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, MLOps, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd8bdf82d729ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5067287c910f6c1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1b51a467a01f2b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f8171dad79d797d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e7fb703deec0d36</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr. Data &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd6170b836318a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3dbe830bdc25c0e6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 – Data Engineer Intern (Charlotte)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbae05545c6868d1</t>
+          <t>https://www.indeed.com/viewjob?jk=801b07c086fc4c1b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Tech &amp; Data Program Summer 2027 - Data Engineer Intern (Chicago)</t>
+          <t>Innovation Engineer- Remote (Anywhere in the U.S.)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>GuidePoint Security</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, MLOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f0621a423908c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2717547230f0b2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer BILH Pharmacy Westwood, Ma, Hybrid / on-site</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Beth Israel Lahey Health</t>
+          <t>Mankato Clinic</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Westwood, MA, US USA</t>
+          <t>Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Data Modeling, ETL, Kubernetes, AKS, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf255b6550fc872f</t>
+          <t>https://www.indeed.com/viewjob?jk=35ca511d20adfc77</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
+          <t>Senior Data Engineer SQL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Unity Catalog, Spark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Spark, Kafka, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
+          <t>https://www.indeed.com/viewjob?jk=01ecd788ad558b31</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Infrastructure Automation Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tapestry</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Spark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a7770f9ee523e2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f8171dad79d797d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d618dcf278adc42</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0147db9614391e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae136048a3d8779</t>
+          <t>https://www.indeed.com/viewjob?jk=045f93f9a84c712a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Connected Vehicle Platform Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Textron Specialized Vehicles</t>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, ETL, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
+          <t>https://www.indeed.com/viewjob?jk=d13f2df622bd87a8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SDN Automation Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b08e7f2c8d072fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=774dd94ebecb0e82</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate Analytics Engineer</t>
+          <t>Senior Data Architect - US</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Databricks, Scala, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522678fc742dc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=90d5d0fa669953e3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Software Engineer</t>
+          <t>Senior Full Stack .NET Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe925ed625c1711</t>
+          <t>https://www.indeed.com/viewjob?jk=e48d48c8e84a2951</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>IT DEVELOPER</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3950e40095baf48</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5bb41689c0fd71</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b84353b55cf1a47</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Cyber Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe925ed625c1711</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Associate Analytics Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>S3, IAM, RDS, Databricks, Scala, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
+          <t>https://www.indeed.com/viewjob?jk=e522678fc742dc7a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, Terraform, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,147 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Collectiv LLC</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47e76c61522acf68</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=98920657e7b757a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>AI LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=512d71dc2c72b295</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6875238a4eff9e2d</t>
         </is>
       </c>
     </row>
